--- a/example1-metabolomics/results-A/pca/pca_norm_MaleMHFD_over_MaleMRD.xlsx
+++ b/example1-metabolomics/results-A/pca/pca_norm_MaleMHFD_over_MaleMRD.xlsx
@@ -506,46 +506,46 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>0.219217933591357</v>
+        <v>0.215846927085042</v>
       </c>
       <c r="C2" t="n">
-        <v>0.150653463755303</v>
+        <v>0.158330572212147</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0182224151984323</v>
+        <v>-0.0338019023151626</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.313815492341254</v>
+        <v>-0.286343461035489</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.220130260991116</v>
+        <v>-0.195188239573026</v>
       </c>
       <c r="G2" t="n">
-        <v>0.580064119237588</v>
+        <v>0.594525271611783</v>
       </c>
       <c r="H2" t="n">
-        <v>0.104817795724234</v>
+        <v>-0.141628097173827</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.204758398552286</v>
+        <v>0.120431879365572</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.164544322073514</v>
+        <v>-0.229315534181696</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0219389288792947</v>
+        <v>0.0236569385298816</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0255843876464907</v>
+        <v>0.0163392959016135</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0204903463144571</v>
+        <v>0.0147177950054215</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.101048335538546</v>
+        <v>-0.120108479544746</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.152910240228075</v>
+        <v>-0.0231876450714125</v>
       </c>
     </row>
     <row r="3">
@@ -553,46 +553,46 @@
         <v>16</v>
       </c>
       <c r="B3" t="n">
-        <v>0.136360218369064</v>
+        <v>0.142357873320927</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0542895563756791</v>
+        <v>0.0388425856186727</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.247544145877942</v>
+        <v>-0.238283145107815</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.325050229272245</v>
+        <v>-0.273679028101084</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0537128942868514</v>
+        <v>0.0837010803746952</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.158225000765953</v>
+        <v>-0.0691451830652687</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.416414414111235</v>
+        <v>0.44422078717084</v>
       </c>
       <c r="I3" t="n">
-        <v>0.352946315103762</v>
+        <v>-0.306225543393065</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0724163504124051</v>
+        <v>0.0808728130762273</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.161455387376145</v>
+        <v>-0.222543714379465</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0537203968893001</v>
+        <v>0.0804999516853426</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0434004314750607</v>
+        <v>0.0558925307595054</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.14984619071566</v>
+        <v>-0.117075306975561</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.322515698879907</v>
+        <v>-0.252578513746314</v>
       </c>
     </row>
     <row r="4">
@@ -600,46 +600,46 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>0.226177707171588</v>
+        <v>0.222045209187688</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.242120752564314</v>
+        <v>-0.234615524100259</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.109261674010362</v>
+        <v>-0.115633531492324</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.215351337806638</v>
+        <v>-0.290310007350309</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.369503357475525</v>
+        <v>-0.361560811109406</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.415716520132491</v>
+        <v>-0.400379143251948</v>
       </c>
       <c r="H4" t="n">
-        <v>0.298881180749089</v>
+        <v>-0.235618643839031</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.128205657947197</v>
+        <v>0.119491970619449</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.260441084308195</v>
+        <v>-0.250887904129201</v>
       </c>
       <c r="K4" t="n">
-        <v>0.14139037753482</v>
+        <v>0.073847022480674</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.166279093815058</v>
+        <v>-0.121935534922535</v>
       </c>
       <c r="M4" t="n">
-        <v>0.164902084350589</v>
+        <v>0.193114741386875</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.133774082172299</v>
+        <v>-0.0982837963313498</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.212013272056055</v>
+        <v>-0.205951796932864</v>
       </c>
     </row>
     <row r="5">
@@ -647,46 +647,46 @@
         <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>0.181178657613231</v>
+        <v>0.174752692431549</v>
       </c>
       <c r="C5" t="n">
-        <v>0.164364781970712</v>
+        <v>0.181635789603346</v>
       </c>
       <c r="D5" t="n">
-        <v>0.150687857692854</v>
+        <v>0.127489701335636</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0572374122176685</v>
+        <v>-0.112964000496452</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.148129006401789</v>
+        <v>-0.151820363321156</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.24154429380465</v>
+        <v>-0.234418064060648</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.226217466186725</v>
+        <v>0.228296849296563</v>
       </c>
       <c r="I5" t="n">
-        <v>0.264369891261447</v>
+        <v>-0.284019194157838</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.180644565070483</v>
+        <v>-0.0499445258418588</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.231330810232795</v>
+        <v>-0.278674409019922</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.170591376621681</v>
+        <v>-0.156778713691701</v>
       </c>
       <c r="M5" t="n">
-        <v>0.257904438705922</v>
+        <v>0.290574990809411</v>
       </c>
       <c r="N5" t="n">
-        <v>0.245578825992788</v>
+        <v>0.210088065006289</v>
       </c>
       <c r="O5" t="n">
-        <v>0.300766597069796</v>
+        <v>0.246319816057912</v>
       </c>
     </row>
     <row r="6">
@@ -694,46 +694,46 @@
         <v>19</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0866200090911231</v>
+        <v>-0.07957089770086</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0933095893118975</v>
+        <v>-0.0856551301505789</v>
       </c>
       <c r="D6" t="n">
-        <v>0.668831050597023</v>
+        <v>0.699471429954304</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0314111259811526</v>
+        <v>-0.0459873812467696</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.555548998353904</v>
+        <v>-0.530871400451817</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0665246589332697</v>
+        <v>0.106572146112555</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.180539893218272</v>
+        <v>0.183936442267633</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.0108397297477871</v>
+        <v>0.05348245045099</v>
       </c>
       <c r="J6" t="n">
-        <v>0.143744359976458</v>
+        <v>0.117791845083449</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0916135589127345</v>
+        <v>-0.0606853046961024</v>
       </c>
       <c r="L6" t="n">
-        <v>0.141695908422333</v>
+        <v>0.137652782190165</v>
       </c>
       <c r="M6" t="n">
-        <v>0.152557968670941</v>
+        <v>0.124282339251588</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.112457206246978</v>
+        <v>-0.114207812181874</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0181124121024817</v>
+        <v>0.00635047195796074</v>
       </c>
     </row>
     <row r="7">
@@ -741,46 +741,46 @@
         <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>0.157939332020269</v>
+        <v>0.159052398999857</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0281097957459383</v>
+        <v>-0.0341754627943184</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.158933649661597</v>
+        <v>-0.15736775370394</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.181074964715734</v>
+        <v>-0.153049368216712</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.00486624757145358</v>
+        <v>0.0106856631503492</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0301348995696497</v>
+        <v>0.0723136275597133</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.102470588446312</v>
+        <v>0.126464028336353</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.346696287503523</v>
+        <v>0.286362511878701</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.13722894446799</v>
+        <v>-0.238854370549509</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0303898014991203</v>
+        <v>0.0352071716595036</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00226736776853491</v>
+        <v>0.00986259273258364</v>
       </c>
       <c r="M7" t="n">
-        <v>0.044543661486442</v>
+        <v>0.0498205253416711</v>
       </c>
       <c r="N7" t="n">
-        <v>0.346602564536075</v>
+        <v>0.34848425723413</v>
       </c>
       <c r="O7" t="n">
-        <v>0.194276826839876</v>
+        <v>0.182974453837105</v>
       </c>
     </row>
     <row r="8">
@@ -788,46 +788,46 @@
         <v>21</v>
       </c>
       <c r="B8" t="n">
-        <v>0.531175536479457</v>
+        <v>0.532237283806098</v>
       </c>
       <c r="C8" t="n">
-        <v>0.588010738090219</v>
+        <v>0.592230566841294</v>
       </c>
       <c r="D8" t="n">
-        <v>0.266577687955242</v>
+        <v>0.253355206059769</v>
       </c>
       <c r="E8" t="n">
-        <v>0.294451195691721</v>
+        <v>0.277333960497724</v>
       </c>
       <c r="F8" t="n">
-        <v>0.135315907935817</v>
+        <v>0.113719531742881</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.110250806736157</v>
+        <v>-0.170468458599696</v>
       </c>
       <c r="H8" t="n">
-        <v>0.27707217967469</v>
+        <v>-0.283488519941337</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0126348531004653</v>
+        <v>-0.0102206278973778</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0316054196841716</v>
+        <v>-0.0364507868350518</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0824265016203187</v>
+        <v>0.0743375283059771</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0508058052398912</v>
+        <v>0.0565852382489417</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.00778046626451108</v>
+        <v>-0.0186361249199041</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0493090890084469</v>
+        <v>-0.0322599123288765</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.107947066964138</v>
+        <v>0.0110332219841818</v>
       </c>
     </row>
     <row r="9">
@@ -835,46 +835,46 @@
         <v>22</v>
       </c>
       <c r="B9" t="n">
-        <v>0.177243070864463</v>
+        <v>0.174071538864637</v>
       </c>
       <c r="C9" t="n">
-        <v>0.174672121049349</v>
+        <v>0.184654825740942</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0685308980726081</v>
+        <v>0.0526097925410433</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.308684962476138</v>
+        <v>-0.311801343755262</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0624768861339407</v>
+        <v>-0.0417677544345186</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0868812713241926</v>
+        <v>-0.0403726808732428</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0398657791795316</v>
+        <v>-0.00202086145452484</v>
       </c>
       <c r="I9" t="n">
-        <v>0.161787895067067</v>
+        <v>-0.0117884353576951</v>
       </c>
       <c r="J9" t="n">
-        <v>0.321847633801746</v>
+        <v>0.401920041594903</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.221334384474273</v>
+        <v>-0.1945179897368</v>
       </c>
       <c r="L9" t="n">
-        <v>0.00909969404627911</v>
+        <v>-0.0131140103263186</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.457222530079436</v>
+        <v>-0.441276986696521</v>
       </c>
       <c r="N9" t="n">
-        <v>0.097389747389566</v>
+        <v>0.106127263430039</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.103553504665172</v>
+        <v>-0.340758873046035</v>
       </c>
     </row>
     <row r="10">
@@ -882,46 +882,46 @@
         <v>23</v>
       </c>
       <c r="B10" t="n">
-        <v>0.10748832826637</v>
+        <v>0.115846382117868</v>
       </c>
       <c r="C10" t="n">
-        <v>0.1091918250171</v>
+        <v>0.0895713863246028</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.146785820434025</v>
+        <v>-0.127234112118448</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.0260599359428166</v>
+        <v>0.0204108332239566</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0512997863667114</v>
+        <v>-0.0391967484366484</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0821565023371183</v>
+        <v>-0.0269311367491475</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.103896072008833</v>
+        <v>0.149466933281956</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.160368450936352</v>
+        <v>0.279945916952982</v>
       </c>
       <c r="J10" t="n">
-        <v>0.443804271346046</v>
+        <v>0.353543915606478</v>
       </c>
       <c r="K10" t="n">
-        <v>0.119108692592279</v>
+        <v>0.19175430720894</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0792553062000116</v>
+        <v>-0.0765613116728451</v>
       </c>
       <c r="M10" t="n">
-        <v>0.297953129623592</v>
+        <v>0.289420222222843</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.238515304271001</v>
+        <v>-0.252488030868628</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.0224202543001321</v>
+        <v>0.148162738765613</v>
       </c>
     </row>
     <row r="11">
@@ -929,46 +929,46 @@
         <v>24</v>
       </c>
       <c r="B11" t="n">
-        <v>0.234864799025424</v>
+        <v>0.222856920131975</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.236791751754658</v>
+        <v>-0.203866317196907</v>
       </c>
       <c r="D11" t="n">
-        <v>0.433578414733656</v>
+        <v>0.409547728162915</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.320471578329539</v>
+        <v>-0.342374350320465</v>
       </c>
       <c r="F11" t="n">
-        <v>0.472093620581195</v>
+        <v>0.492560639666733</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.202954248636604</v>
+        <v>-0.181369703232321</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.269219972383992</v>
+        <v>0.283614471270956</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.329493428728647</v>
+        <v>0.224871970396822</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.068069031974357</v>
+        <v>-0.210680091859365</v>
       </c>
       <c r="K11" t="n">
-        <v>0.246335887823794</v>
+        <v>0.275180846017886</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0310033879506138</v>
+        <v>0.0140261861814822</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.11062810589875</v>
+        <v>-0.124604661786539</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0402625235974067</v>
+        <v>-0.0496126651599571</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0676585214058838</v>
+        <v>-0.00523806764608067</v>
       </c>
     </row>
     <row r="12">
@@ -976,46 +976,46 @@
         <v>25</v>
       </c>
       <c r="B12" t="n">
-        <v>0.159554687873944</v>
+        <v>0.14908765723754</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0272231096650571</v>
+        <v>0.0440935103685852</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.149317875294659</v>
+        <v>-0.183681823213411</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.233392635301268</v>
+        <v>-0.278731070293169</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.122130043420784</v>
+        <v>-0.120217969259232</v>
       </c>
       <c r="G12" t="n">
-        <v>0.124817825855758</v>
+        <v>0.105097707251005</v>
       </c>
       <c r="H12" t="n">
-        <v>0.101259503981105</v>
+        <v>-0.133837404290111</v>
       </c>
       <c r="I12" t="n">
-        <v>0.294399171349591</v>
+        <v>-0.36518505906704</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.222341458223902</v>
+        <v>-0.121019096310653</v>
       </c>
       <c r="K12" t="n">
-        <v>0.332387305953894</v>
+        <v>0.253860591543782</v>
       </c>
       <c r="L12" t="n">
-        <v>0.373084912341287</v>
+        <v>0.392021210994278</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0670626393497527</v>
+        <v>0.0766175790013979</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.167548256149377</v>
+        <v>-0.187576633143931</v>
       </c>
       <c r="O12" t="n">
-        <v>0.371849703895832</v>
+        <v>-0.00717483333463958</v>
       </c>
     </row>
     <row r="13">
@@ -1023,46 +1023,46 @@
         <v>26</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0600708069226081</v>
+        <v>0.0645788923940831</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0808874994728175</v>
+        <v>0.0675142800916422</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.140596186061923</v>
+        <v>-0.131264580405616</v>
       </c>
       <c r="E13" t="n">
-        <v>0.146552125563653</v>
+        <v>0.148289034234336</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.157706406469216</v>
+        <v>-0.167003673071234</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.111628294563971</v>
+        <v>-0.0947416618186645</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.261682246791939</v>
+        <v>0.268292051979079</v>
       </c>
       <c r="I13" t="n">
-        <v>0.00290761482959327</v>
+        <v>-0.0298253581678912</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0245995923360814</v>
+        <v>0.0040082419858059</v>
       </c>
       <c r="K13" t="n">
-        <v>0.221968444139511</v>
+        <v>0.217220462814807</v>
       </c>
       <c r="L13" t="n">
-        <v>0.543267283521346</v>
+        <v>0.54157392887316</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.161348870488438</v>
+        <v>-0.179465612064926</v>
       </c>
       <c r="N13" t="n">
-        <v>0.243501609272667</v>
+        <v>0.243674795961549</v>
       </c>
       <c r="O13" t="n">
-        <v>0.128845634611074</v>
+        <v>0.193062392869655</v>
       </c>
     </row>
     <row r="14">
@@ -1070,46 +1070,46 @@
         <v>27</v>
       </c>
       <c r="B14" t="n">
-        <v>0.26142022264744</v>
+        <v>0.260756120133608</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.114675822423592</v>
+        <v>-0.114826336107827</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0496703268596838</v>
+        <v>-0.0461855256175216</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0534227304393962</v>
+        <v>-0.0449630911184901</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0142067004075194</v>
+        <v>0.0197322937055839</v>
       </c>
       <c r="G14" t="n">
-        <v>0.174292277605342</v>
+        <v>0.175721141914575</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.107438293575051</v>
+        <v>0.0785926617724264</v>
       </c>
       <c r="I14" t="n">
-        <v>0.203848722289381</v>
+        <v>-0.180664654492363</v>
       </c>
       <c r="J14" t="n">
-        <v>0.0766598648580447</v>
+        <v>0.139980357692313</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.169020137246317</v>
+        <v>-0.159909298545819</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.217977185378235</v>
+        <v>-0.223475628962178</v>
       </c>
       <c r="M14" t="n">
-        <v>0.0885921516372484</v>
+        <v>0.104729550114256</v>
       </c>
       <c r="N14" t="n">
-        <v>0.203639299817504</v>
+        <v>0.182804416439654</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.00610725720376667</v>
+        <v>0.311732524622079</v>
       </c>
     </row>
     <row r="15">
@@ -1117,46 +1117,46 @@
         <v>28</v>
       </c>
       <c r="B15" t="n">
-        <v>0.125380069691246</v>
+        <v>0.139411439049055</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.0930864501253389</v>
+        <v>-0.120571055087782</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0110337895062274</v>
+        <v>0.0572685183136997</v>
       </c>
       <c r="E15" t="n">
-        <v>0.245350354868465</v>
+        <v>0.318904661451976</v>
       </c>
       <c r="F15" t="n">
-        <v>0.0561396264922218</v>
+        <v>0.05917268028887</v>
       </c>
       <c r="G15" t="n">
-        <v>0.27733212154312</v>
+        <v>0.281411954564269</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.243350408043506</v>
+        <v>0.204955274151126</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.0338875710437363</v>
+        <v>-0.00672617777430144</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.0203880325957641</v>
+        <v>-0.072294788495634</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0370799508205972</v>
+        <v>-0.0182351751340084</v>
       </c>
       <c r="L15" t="n">
-        <v>0.135927730890598</v>
+        <v>0.132091860206335</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0820940881222186</v>
+        <v>0.0416173457410543</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0986230049777604</v>
+        <v>-0.0762126067800062</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.0129759242018522</v>
+        <v>-0.46655024392967</v>
       </c>
     </row>
     <row r="16">
@@ -1164,46 +1164,46 @@
         <v>29</v>
       </c>
       <c r="B16" t="n">
-        <v>0.115278687636521</v>
+        <v>0.125130980090137</v>
       </c>
       <c r="C16" t="n">
-        <v>0.117266307614709</v>
+        <v>0.0945944794166881</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.174332808119947</v>
+        <v>-0.151293083181801</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.0529547637641877</v>
+        <v>0.00757416009827086</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.040320957103986</v>
+        <v>-0.0244552663377533</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.0111037965175065</v>
+        <v>0.0467212853813919</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0796522634466623</v>
+        <v>0.120620914139684</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.138850483188957</v>
+        <v>0.25594090762474</v>
       </c>
       <c r="J16" t="n">
-        <v>0.376510896837548</v>
+        <v>0.307468748521002</v>
       </c>
       <c r="K16" t="n">
-        <v>0.00529921345288856</v>
+        <v>0.0676327466349073</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.223111466558148</v>
+        <v>-0.218860509442088</v>
       </c>
       <c r="M16" t="n">
-        <v>0.167234045059127</v>
+        <v>0.169385191482912</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0751127613137639</v>
+        <v>-0.0678834266741262</v>
       </c>
       <c r="O16" t="n">
-        <v>0.525942463292268</v>
+        <v>-0.242373176139405</v>
       </c>
     </row>
     <row r="17">
@@ -1211,46 +1211,46 @@
         <v>30</v>
       </c>
       <c r="B17" t="n">
-        <v>0.276651960782342</v>
+        <v>0.275814164179018</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.236912997666884</v>
+        <v>-0.237524343412188</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0169661240993072</v>
+        <v>-0.00745780166748161</v>
       </c>
       <c r="E17" t="n">
-        <v>0.171027597920858</v>
+        <v>0.158994250931865</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0242123977722134</v>
+        <v>0.0122168432228338</v>
       </c>
       <c r="G17" t="n">
-        <v>0.20798433686239</v>
+        <v>0.158207053372805</v>
       </c>
       <c r="H17" t="n">
-        <v>0.0955571612444445</v>
+        <v>-0.141393630461808</v>
       </c>
       <c r="I17" t="n">
-        <v>0.0347640416312321</v>
+        <v>-0.0700331775058513</v>
       </c>
       <c r="J17" t="n">
-        <v>0.00850567987268043</v>
+        <v>-0.0135652825865529</v>
       </c>
       <c r="K17" t="n">
-        <v>0.062403008408698</v>
+        <v>0.0783743832598784</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.240502000835411</v>
+        <v>-0.244167962923406</v>
       </c>
       <c r="M17" t="n">
-        <v>0.10967043852133</v>
+        <v>0.115069899679326</v>
       </c>
       <c r="N17" t="n">
-        <v>0.142710104511462</v>
+        <v>0.131671944323397</v>
       </c>
       <c r="O17" t="n">
-        <v>0.0444711665102833</v>
+        <v>-0.0694956212355509</v>
       </c>
     </row>
     <row r="18">
@@ -1258,46 +1258,46 @@
         <v>31</v>
       </c>
       <c r="B18" t="n">
-        <v>0.148039395645731</v>
+        <v>0.145339155313546</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0641365528209727</v>
+        <v>-0.0674987163592472</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.215334490715395</v>
+        <v>-0.219206723109521</v>
       </c>
       <c r="E18" t="n">
-        <v>0.181454471240034</v>
+        <v>0.135207539392561</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.241875500553571</v>
+        <v>-0.263298672547318</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.223950026729497</v>
+        <v>-0.222612395229574</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.132054805046338</v>
+        <v>0.15981299531325</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.214451827101865</v>
+        <v>0.236491601563914</v>
       </c>
       <c r="J18" t="n">
-        <v>0.272347063556133</v>
+        <v>0.176834267044835</v>
       </c>
       <c r="K18" t="n">
-        <v>0.120160222444956</v>
+        <v>0.187357780947447</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0944418851777116</v>
+        <v>0.0619210266005432</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.110712411451209</v>
+        <v>-0.121526813427054</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.173687203174489</v>
+        <v>-0.2164160898228</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.160006349302111</v>
+        <v>0.137329240096882</v>
       </c>
     </row>
     <row r="19">
@@ -1305,46 +1305,46 @@
         <v>32</v>
       </c>
       <c r="B19" t="n">
-        <v>0.108335700150131</v>
+        <v>0.118720868348221</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.050000263946987</v>
+        <v>-0.0702180896730348</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0344597069345822</v>
+        <v>-0.00262473429142883</v>
       </c>
       <c r="E19" t="n">
-        <v>0.0635032589284973</v>
+        <v>0.112809168709506</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0309326549330949</v>
+        <v>-0.0212007554496724</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0546966184547378</v>
+        <v>0.0830897094220322</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.0779734923113725</v>
+        <v>0.0885724243755241</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0978681954087723</v>
+        <v>0.13285111810426</v>
       </c>
       <c r="J19" t="n">
-        <v>0.121572762787166</v>
+        <v>0.0669125564245377</v>
       </c>
       <c r="K19" t="n">
-        <v>0.0674559794968847</v>
+        <v>0.08768816951633</v>
       </c>
       <c r="L19" t="n">
-        <v>0.177856030481413</v>
+        <v>0.199742435560485</v>
       </c>
       <c r="M19" t="n">
-        <v>0.331352855160074</v>
+        <v>0.32580783999144</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5550191838502</v>
+        <v>0.55079778598757</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.408900216608421</v>
+        <v>-0.279167221210723</v>
       </c>
     </row>
     <row r="20">
@@ -1352,46 +1352,46 @@
         <v>33</v>
       </c>
       <c r="B20" t="n">
-        <v>0.259124578956307</v>
+        <v>0.259680876775407</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.289419570111147</v>
+        <v>-0.295061338319742</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0588420455075382</v>
+        <v>-0.0431779618025824</v>
       </c>
       <c r="E20" t="n">
-        <v>0.386848143984349</v>
+        <v>0.346548696971334</v>
       </c>
       <c r="F20" t="n">
-        <v>0.00541956690653946</v>
+        <v>-0.0246642251819949</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.153846154079177</v>
+        <v>-0.206589433209265</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0182903763294374</v>
+        <v>0.00172929303744773</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0492962338521912</v>
+        <v>-0.0122322647174007</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.26115497688166</v>
+        <v>-0.237170125191476</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.416545126338111</v>
+        <v>-0.426174177982837</v>
       </c>
       <c r="L20" t="n">
-        <v>0.169199491203654</v>
+        <v>0.144527026903605</v>
       </c>
       <c r="M20" t="n">
-        <v>0.00652811976154438</v>
+        <v>-0.0286329543404284</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.194143984986188</v>
+        <v>-0.217506054355344</v>
       </c>
       <c r="O20" t="n">
-        <v>0.111288361743764</v>
+        <v>-0.10277999498754</v>
       </c>
     </row>
     <row r="21">
@@ -1399,46 +1399,46 @@
         <v>34</v>
       </c>
       <c r="B21" t="n">
-        <v>0.158221148166019</v>
+        <v>0.159135599356526</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0911942331493307</v>
+        <v>-0.0952818793071476</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0733632697539495</v>
+        <v>-0.0659613507267245</v>
       </c>
       <c r="E21" t="n">
-        <v>0.0533194415612919</v>
+        <v>0.035705575448106</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.311143213474281</v>
+        <v>-0.314450692878198</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0529847839983312</v>
+        <v>0.0572388896269371</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0412389999525255</v>
+        <v>0.043530579241622</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.177609740784177</v>
+        <v>0.144218909146718</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0460341872794184</v>
+        <v>-0.0967460240855595</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.102579114831951</v>
+        <v>-0.0830921955722669</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.175974515462603</v>
+        <v>-0.202351285295147</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.574330123556652</v>
+        <v>-0.568026717002782</v>
       </c>
       <c r="N21" t="n">
-        <v>0.173344818028868</v>
+        <v>0.209154797492692</v>
       </c>
       <c r="O21" t="n">
-        <v>0.115718083503853</v>
+        <v>0.0557573885947905</v>
       </c>
     </row>
     <row r="22">
@@ -1446,46 +1446,46 @@
         <v>35</v>
       </c>
       <c r="B22" t="n">
-        <v>0.152787386058832</v>
+        <v>0.162778096759559</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.137824586376396</v>
+        <v>-0.156414327179443</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0559835762338327</v>
+        <v>-0.0237774801997158</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.208462880053805</v>
+        <v>-0.126612377416408</v>
       </c>
       <c r="F22" t="n">
-        <v>0.170529201946443</v>
+        <v>0.203311596912646</v>
       </c>
       <c r="G22" t="n">
-        <v>0.101814352796228</v>
+        <v>0.157501218584994</v>
       </c>
       <c r="H22" t="n">
-        <v>0.212738991389158</v>
+        <v>-0.167798758571628</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.172835883832171</v>
+        <v>0.329555655133222</v>
       </c>
       <c r="J22" t="n">
-        <v>0.205556918039189</v>
+        <v>0.199051961647002</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.527536272129893</v>
+        <v>-0.484864785814726</v>
       </c>
       <c r="L22" t="n">
-        <v>0.393291915658486</v>
+        <v>0.380318840174791</v>
       </c>
       <c r="M22" t="n">
-        <v>0.107736182081379</v>
+        <v>0.0622325029136213</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.131760437413266</v>
+        <v>-0.138380705679686</v>
       </c>
       <c r="O22" t="n">
-        <v>0.0440212788657281</v>
+        <v>0.294224491711368</v>
       </c>
     </row>
     <row r="23">
@@ -1493,46 +1493,46 @@
         <v>36</v>
       </c>
       <c r="B23" t="n">
-        <v>0.164737001756311</v>
+        <v>0.161589330464693</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.44281713307566</v>
+        <v>-0.433819869658525</v>
       </c>
       <c r="D23" t="n">
-        <v>0.10476123787101</v>
+        <v>0.113831094227598</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0120428852219869</v>
+        <v>-0.0530742949290581</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0464141512740765</v>
+        <v>0.0456630449007295</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0247160160881914</v>
+        <v>-0.0666785131883262</v>
       </c>
       <c r="H23" t="n">
-        <v>0.345381405350216</v>
+        <v>-0.36044929054247</v>
       </c>
       <c r="I23" t="n">
-        <v>0.403459317903965</v>
+        <v>-0.270295922520253</v>
       </c>
       <c r="J23" t="n">
-        <v>0.348833900829294</v>
+        <v>0.44391363034526</v>
       </c>
       <c r="K23" t="n">
-        <v>0.204958138935256</v>
+        <v>0.210187285700342</v>
       </c>
       <c r="L23" t="n">
-        <v>0.101380305638861</v>
+        <v>0.108042559207978</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.0518184841794709</v>
+        <v>-0.042417068484735</v>
       </c>
       <c r="N23" t="n">
-        <v>0.143218516709989</v>
+        <v>0.148775196682363</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0590279228689319</v>
+        <v>0.0293950711900953</v>
       </c>
     </row>
     <row r="24">
@@ -1540,46 +1540,46 @@
         <v>37</v>
       </c>
       <c r="B24" t="n">
-        <v>0.239531393365342</v>
+        <v>0.242625712743089</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.149016876846476</v>
+        <v>-0.156781818638575</v>
       </c>
       <c r="D24" t="n">
-        <v>0.00342394976238209</v>
+        <v>0.0207468132557925</v>
       </c>
       <c r="E24" t="n">
-        <v>0.151513291291156</v>
+        <v>0.169682046910329</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0303211578171265</v>
+        <v>0.0262250268834016</v>
       </c>
       <c r="G24" t="n">
-        <v>0.255027031234592</v>
+        <v>0.237978951606792</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.339576437676604</v>
+        <v>0.275715905489834</v>
       </c>
       <c r="I24" t="n">
-        <v>0.18486553492461</v>
+        <v>-0.263047846416108</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0128698376781155</v>
+        <v>0.00433479490687868</v>
       </c>
       <c r="K24" t="n">
-        <v>0.207456178016546</v>
+        <v>0.217205977593074</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.19150409398834</v>
+        <v>-0.203852140337</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.131331114289047</v>
+        <v>-0.140940968554306</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.278440180998825</v>
+        <v>-0.258427380190702</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.118290019879757</v>
+        <v>0.217244617915519</v>
       </c>
     </row>
   </sheetData>

--- a/example1-metabolomics/results-A/pca/pca_norm_MaleMHFD_over_MaleMRD.xlsx
+++ b/example1-metabolomics/results-A/pca/pca_norm_MaleMHFD_over_MaleMRD.xlsx
@@ -506,46 +506,46 @@
         <v>15</v>
       </c>
       <c r="B2" t="n">
-        <v>0.215846927085042</v>
+        <v>0.219217933591357</v>
       </c>
       <c r="C2" t="n">
-        <v>0.158330572212147</v>
+        <v>0.150653463755303</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.0338019023151626</v>
+        <v>-0.0182224151984323</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.286343461035489</v>
+        <v>-0.313815492341254</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.195188239573026</v>
+        <v>-0.220130260991116</v>
       </c>
       <c r="G2" t="n">
-        <v>0.594525271611783</v>
+        <v>0.580064119237588</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.141628097173827</v>
+        <v>0.104817795724234</v>
       </c>
       <c r="I2" t="n">
-        <v>0.120431879365572</v>
+        <v>-0.204758398552286</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.229315534181696</v>
+        <v>-0.164544322073514</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0236569385298816</v>
+        <v>0.0219389288792947</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0163392959016135</v>
+        <v>0.0255843876464907</v>
       </c>
       <c r="M2" t="n">
-        <v>0.0147177950054215</v>
+        <v>0.0204903463144571</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.120108479544746</v>
+        <v>-0.101048335538546</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0231876450714125</v>
+        <v>-0.152910240228075</v>
       </c>
     </row>
     <row r="3">
@@ -553,46 +553,46 @@
         <v>16</v>
       </c>
       <c r="B3" t="n">
-        <v>0.142357873320927</v>
+        <v>0.136360218369064</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0388425856186727</v>
+        <v>0.0542895563756791</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.238283145107815</v>
+        <v>-0.247544145877942</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.273679028101084</v>
+        <v>-0.325050229272245</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0837010803746952</v>
+        <v>0.0537128942868514</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0691451830652687</v>
+        <v>-0.158225000765953</v>
       </c>
       <c r="H3" t="n">
-        <v>0.44422078717084</v>
+        <v>-0.416414414111235</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.306225543393065</v>
+        <v>0.352946315103762</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0808728130762273</v>
+        <v>-0.0724163504124051</v>
       </c>
       <c r="K3" t="n">
-        <v>-0.222543714379465</v>
+        <v>-0.161455387376145</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0804999516853426</v>
+        <v>0.0537203968893001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0558925307595054</v>
+        <v>0.0434004314750607</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.117075306975561</v>
+        <v>-0.14984619071566</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.252578513746314</v>
+        <v>-0.322515698879907</v>
       </c>
     </row>
     <row r="4">
@@ -600,46 +600,46 @@
         <v>17</v>
       </c>
       <c r="B4" t="n">
-        <v>0.222045209187688</v>
+        <v>0.226177707171588</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.234615524100259</v>
+        <v>-0.242120752564314</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.115633531492324</v>
+        <v>-0.109261674010362</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.290310007350309</v>
+        <v>-0.215351337806638</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.361560811109406</v>
+        <v>-0.369503357475525</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.400379143251948</v>
+        <v>-0.415716520132491</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.235618643839031</v>
+        <v>0.298881180749089</v>
       </c>
       <c r="I4" t="n">
-        <v>0.119491970619449</v>
+        <v>-0.128205657947197</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.250887904129201</v>
+        <v>-0.260441084308195</v>
       </c>
       <c r="K4" t="n">
-        <v>0.073847022480674</v>
+        <v>0.14139037753482</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.121935534922535</v>
+        <v>-0.166279093815058</v>
       </c>
       <c r="M4" t="n">
-        <v>0.193114741386875</v>
+        <v>0.164902084350589</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0982837963313498</v>
+        <v>-0.133774082172299</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.205951796932864</v>
+        <v>-0.212013272056055</v>
       </c>
     </row>
     <row r="5">
@@ -647,46 +647,46 @@
         <v>18</v>
       </c>
       <c r="B5" t="n">
-        <v>0.174752692431549</v>
+        <v>0.181178657613231</v>
       </c>
       <c r="C5" t="n">
-        <v>0.181635789603346</v>
+        <v>0.164364781970712</v>
       </c>
       <c r="D5" t="n">
-        <v>0.127489701335636</v>
+        <v>0.150687857692854</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.112964000496452</v>
+        <v>-0.0572374122176685</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.151820363321156</v>
+        <v>-0.148129006401789</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.234418064060648</v>
+        <v>-0.24154429380465</v>
       </c>
       <c r="H5" t="n">
-        <v>0.228296849296563</v>
+        <v>-0.226217466186725</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.284019194157838</v>
+        <v>0.264369891261447</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.0499445258418588</v>
+        <v>-0.180644565070483</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.278674409019922</v>
+        <v>-0.231330810232795</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.156778713691701</v>
+        <v>-0.170591376621681</v>
       </c>
       <c r="M5" t="n">
-        <v>0.290574990809411</v>
+        <v>0.257904438705922</v>
       </c>
       <c r="N5" t="n">
-        <v>0.210088065006289</v>
+        <v>0.245578825992788</v>
       </c>
       <c r="O5" t="n">
-        <v>0.246319816057912</v>
+        <v>0.300766597069796</v>
       </c>
     </row>
     <row r="6">
@@ -694,46 +694,46 @@
         <v>19</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.07957089770086</v>
+        <v>-0.0866200090911231</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.0856551301505789</v>
+        <v>-0.0933095893118975</v>
       </c>
       <c r="D6" t="n">
-        <v>0.699471429954304</v>
+        <v>0.668831050597023</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0459873812467696</v>
+        <v>-0.0314111259811526</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.530871400451817</v>
+        <v>-0.555548998353904</v>
       </c>
       <c r="G6" t="n">
-        <v>0.106572146112555</v>
+        <v>0.0665246589332697</v>
       </c>
       <c r="H6" t="n">
-        <v>0.183936442267633</v>
+        <v>-0.180539893218272</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05348245045099</v>
+        <v>-0.0108397297477871</v>
       </c>
       <c r="J6" t="n">
-        <v>0.117791845083449</v>
+        <v>0.143744359976458</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0606853046961024</v>
+        <v>-0.0916135589127345</v>
       </c>
       <c r="L6" t="n">
-        <v>0.137652782190165</v>
+        <v>0.141695908422333</v>
       </c>
       <c r="M6" t="n">
-        <v>0.124282339251588</v>
+        <v>0.152557968670941</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.114207812181874</v>
+        <v>-0.112457206246978</v>
       </c>
       <c r="O6" t="n">
-        <v>0.00635047195796074</v>
+        <v>0.0181124121024817</v>
       </c>
     </row>
     <row r="7">
@@ -741,46 +741,46 @@
         <v>20</v>
       </c>
       <c r="B7" t="n">
-        <v>0.159052398999857</v>
+        <v>0.157939332020269</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.0341754627943184</v>
+        <v>-0.0281097957459383</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.15736775370394</v>
+        <v>-0.158933649661597</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.153049368216712</v>
+        <v>-0.181074964715734</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0106856631503492</v>
+        <v>-0.00486624757145358</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0723136275597133</v>
+        <v>0.0301348995696497</v>
       </c>
       <c r="H7" t="n">
-        <v>0.126464028336353</v>
+        <v>-0.102470588446312</v>
       </c>
       <c r="I7" t="n">
-        <v>0.286362511878701</v>
+        <v>-0.346696287503523</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.238854370549509</v>
+        <v>-0.13722894446799</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0352071716595036</v>
+        <v>0.0303898014991203</v>
       </c>
       <c r="L7" t="n">
-        <v>0.00986259273258364</v>
+        <v>0.00226736776853491</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0498205253416711</v>
+        <v>0.044543661486442</v>
       </c>
       <c r="N7" t="n">
-        <v>0.34848425723413</v>
+        <v>0.346602564536075</v>
       </c>
       <c r="O7" t="n">
-        <v>0.182974453837105</v>
+        <v>0.194276826839876</v>
       </c>
     </row>
     <row r="8">
@@ -788,46 +788,46 @@
         <v>21</v>
       </c>
       <c r="B8" t="n">
-        <v>0.532237283806098</v>
+        <v>0.531175536479457</v>
       </c>
       <c r="C8" t="n">
-        <v>0.592230566841294</v>
+        <v>0.588010738090219</v>
       </c>
       <c r="D8" t="n">
-        <v>0.253355206059769</v>
+        <v>0.266577687955242</v>
       </c>
       <c r="E8" t="n">
-        <v>0.277333960497724</v>
+        <v>0.294451195691721</v>
       </c>
       <c r="F8" t="n">
-        <v>0.113719531742881</v>
+        <v>0.135315907935817</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.170468458599696</v>
+        <v>-0.110250806736157</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.283488519941337</v>
+        <v>0.27707217967469</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0102206278973778</v>
+        <v>0.0126348531004653</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0364507868350518</v>
+        <v>-0.0316054196841716</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0743375283059771</v>
+        <v>0.0824265016203187</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0565852382489417</v>
+        <v>0.0508058052398912</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0186361249199041</v>
+        <v>-0.00778046626451108</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0322599123288765</v>
+        <v>-0.0493090890084469</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0110332219841818</v>
+        <v>-0.107947066964138</v>
       </c>
     </row>
     <row r="9">
@@ -835,46 +835,46 @@
         <v>22</v>
       </c>
       <c r="B9" t="n">
-        <v>0.174071538864637</v>
+        <v>0.177243070864463</v>
       </c>
       <c r="C9" t="n">
-        <v>0.184654825740942</v>
+        <v>0.174672121049349</v>
       </c>
       <c r="D9" t="n">
-        <v>0.0526097925410433</v>
+        <v>0.0685308980726081</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.311801343755262</v>
+        <v>-0.308684962476138</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.0417677544345186</v>
+        <v>-0.0624768861339407</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0403726808732428</v>
+        <v>-0.0868812713241926</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.00202086145452484</v>
+        <v>0.0398657791795316</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0117884353576951</v>
+        <v>0.161787895067067</v>
       </c>
       <c r="J9" t="n">
-        <v>0.401920041594903</v>
+        <v>0.321847633801746</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.1945179897368</v>
+        <v>-0.221334384474273</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0131140103263186</v>
+        <v>0.00909969404627911</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.441276986696521</v>
+        <v>-0.457222530079436</v>
       </c>
       <c r="N9" t="n">
-        <v>0.106127263430039</v>
+        <v>0.097389747389566</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.340758873046035</v>
+        <v>-0.103553504665172</v>
       </c>
     </row>
     <row r="10">
@@ -882,46 +882,46 @@
         <v>23</v>
       </c>
       <c r="B10" t="n">
-        <v>0.115846382117868</v>
+        <v>0.10748832826637</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0895713863246028</v>
+        <v>0.1091918250171</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.127234112118448</v>
+        <v>-0.146785820434025</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0204108332239566</v>
+        <v>-0.0260599359428166</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0391967484366484</v>
+        <v>-0.0512997863667114</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0269311367491475</v>
+        <v>-0.0821565023371183</v>
       </c>
       <c r="H10" t="n">
-        <v>0.149466933281956</v>
+        <v>-0.103896072008833</v>
       </c>
       <c r="I10" t="n">
-        <v>0.279945916952982</v>
+        <v>-0.160368450936352</v>
       </c>
       <c r="J10" t="n">
-        <v>0.353543915606478</v>
+        <v>0.443804271346046</v>
       </c>
       <c r="K10" t="n">
-        <v>0.19175430720894</v>
+        <v>0.119108692592279</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.0765613116728451</v>
+        <v>-0.0792553062000116</v>
       </c>
       <c r="M10" t="n">
-        <v>0.289420222222843</v>
+        <v>0.297953129623592</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.252488030868628</v>
+        <v>-0.238515304271001</v>
       </c>
       <c r="O10" t="n">
-        <v>0.148162738765613</v>
+        <v>-0.0224202543001321</v>
       </c>
     </row>
     <row r="11">
@@ -929,46 +929,46 @@
         <v>24</v>
       </c>
       <c r="B11" t="n">
-        <v>0.222856920131975</v>
+        <v>0.234864799025424</v>
       </c>
       <c r="C11" t="n">
-        <v>-0.203866317196907</v>
+        <v>-0.236791751754658</v>
       </c>
       <c r="D11" t="n">
-        <v>0.409547728162915</v>
+        <v>0.433578414733656</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.342374350320465</v>
+        <v>-0.320471578329539</v>
       </c>
       <c r="F11" t="n">
-        <v>0.492560639666733</v>
+        <v>0.472093620581195</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.181369703232321</v>
+        <v>-0.202954248636604</v>
       </c>
       <c r="H11" t="n">
-        <v>0.283614471270956</v>
+        <v>-0.269219972383992</v>
       </c>
       <c r="I11" t="n">
-        <v>0.224871970396822</v>
+        <v>-0.329493428728647</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.210680091859365</v>
+        <v>-0.068069031974357</v>
       </c>
       <c r="K11" t="n">
-        <v>0.275180846017886</v>
+        <v>0.246335887823794</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0140261861814822</v>
+        <v>0.0310033879506138</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.124604661786539</v>
+        <v>-0.11062810589875</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0496126651599571</v>
+        <v>-0.0402625235974067</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.00523806764608067</v>
+        <v>0.0676585214058838</v>
       </c>
     </row>
     <row r="12">
@@ -976,46 +976,46 @@
         <v>25</v>
       </c>
       <c r="B12" t="n">
-        <v>0.14908765723754</v>
+        <v>0.159554687873944</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0440935103685852</v>
+        <v>0.0272231096650571</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.183681823213411</v>
+        <v>-0.149317875294659</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.278731070293169</v>
+        <v>-0.233392635301268</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.120217969259232</v>
+        <v>-0.122130043420784</v>
       </c>
       <c r="G12" t="n">
-        <v>0.105097707251005</v>
+        <v>0.124817825855758</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.133837404290111</v>
+        <v>0.101259503981105</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.36518505906704</v>
+        <v>0.294399171349591</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.121019096310653</v>
+        <v>-0.222341458223902</v>
       </c>
       <c r="K12" t="n">
-        <v>0.253860591543782</v>
+        <v>0.332387305953894</v>
       </c>
       <c r="L12" t="n">
-        <v>0.392021210994278</v>
+        <v>0.373084912341287</v>
       </c>
       <c r="M12" t="n">
-        <v>0.0766175790013979</v>
+        <v>0.0670626393497527</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.187576633143931</v>
+        <v>-0.167548256149377</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.00717483333463958</v>
+        <v>0.371849703895832</v>
       </c>
     </row>
     <row r="13">
@@ -1023,46 +1023,46 @@
         <v>26</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0645788923940831</v>
+        <v>0.0600708069226081</v>
       </c>
       <c r="C13" t="n">
-        <v>0.0675142800916422</v>
+        <v>0.0808874994728175</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.131264580405616</v>
+        <v>-0.140596186061923</v>
       </c>
       <c r="E13" t="n">
-        <v>0.148289034234336</v>
+        <v>0.146552125563653</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.167003673071234</v>
+        <v>-0.157706406469216</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0947416618186645</v>
+        <v>-0.111628294563971</v>
       </c>
       <c r="H13" t="n">
-        <v>0.268292051979079</v>
+        <v>-0.261682246791939</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.0298253581678912</v>
+        <v>0.00290761482959327</v>
       </c>
       <c r="J13" t="n">
-        <v>0.0040082419858059</v>
+        <v>0.0245995923360814</v>
       </c>
       <c r="K13" t="n">
-        <v>0.217220462814807</v>
+        <v>0.221968444139511</v>
       </c>
       <c r="L13" t="n">
-        <v>0.54157392887316</v>
+        <v>0.543267283521346</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.179465612064926</v>
+        <v>-0.161348870488438</v>
       </c>
       <c r="N13" t="n">
-        <v>0.243674795961549</v>
+        <v>0.243501609272667</v>
       </c>
       <c r="O13" t="n">
-        <v>0.193062392869655</v>
+        <v>0.128845634611074</v>
       </c>
     </row>
     <row r="14">
@@ -1070,46 +1070,46 @@
         <v>27</v>
       </c>
       <c r="B14" t="n">
-        <v>0.260756120133608</v>
+        <v>0.26142022264744</v>
       </c>
       <c r="C14" t="n">
-        <v>-0.114826336107827</v>
+        <v>-0.114675822423592</v>
       </c>
       <c r="D14" t="n">
-        <v>-0.0461855256175216</v>
+        <v>-0.0496703268596838</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.0449630911184901</v>
+        <v>-0.0534227304393962</v>
       </c>
       <c r="F14" t="n">
-        <v>0.0197322937055839</v>
+        <v>0.0142067004075194</v>
       </c>
       <c r="G14" t="n">
-        <v>0.175721141914575</v>
+        <v>0.174292277605342</v>
       </c>
       <c r="H14" t="n">
-        <v>0.0785926617724264</v>
+        <v>-0.107438293575051</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.180664654492363</v>
+        <v>0.203848722289381</v>
       </c>
       <c r="J14" t="n">
-        <v>0.139980357692313</v>
+        <v>0.0766598648580447</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.159909298545819</v>
+        <v>-0.169020137246317</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.223475628962178</v>
+        <v>-0.217977185378235</v>
       </c>
       <c r="M14" t="n">
-        <v>0.104729550114256</v>
+        <v>0.0885921516372484</v>
       </c>
       <c r="N14" t="n">
-        <v>0.182804416439654</v>
+        <v>0.203639299817504</v>
       </c>
       <c r="O14" t="n">
-        <v>0.311732524622079</v>
+        <v>-0.00610725720376667</v>
       </c>
     </row>
     <row r="15">
@@ -1117,46 +1117,46 @@
         <v>28</v>
       </c>
       <c r="B15" t="n">
-        <v>0.139411439049055</v>
+        <v>0.125380069691246</v>
       </c>
       <c r="C15" t="n">
-        <v>-0.120571055087782</v>
+        <v>-0.0930864501253389</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0572685183136997</v>
+        <v>0.0110337895062274</v>
       </c>
       <c r="E15" t="n">
-        <v>0.318904661451976</v>
+        <v>0.245350354868465</v>
       </c>
       <c r="F15" t="n">
-        <v>0.05917268028887</v>
+        <v>0.0561396264922218</v>
       </c>
       <c r="G15" t="n">
-        <v>0.281411954564269</v>
+        <v>0.27733212154312</v>
       </c>
       <c r="H15" t="n">
-        <v>0.204955274151126</v>
+        <v>-0.243350408043506</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.00672617777430144</v>
+        <v>-0.0338875710437363</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.072294788495634</v>
+        <v>-0.0203880325957641</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0182351751340084</v>
+        <v>-0.0370799508205972</v>
       </c>
       <c r="L15" t="n">
-        <v>0.132091860206335</v>
+        <v>0.135927730890598</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0416173457410543</v>
+        <v>0.0820940881222186</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.0762126067800062</v>
+        <v>-0.0986230049777604</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.46655024392967</v>
+        <v>-0.0129759242018522</v>
       </c>
     </row>
     <row r="16">
@@ -1164,46 +1164,46 @@
         <v>29</v>
       </c>
       <c r="B16" t="n">
-        <v>0.125130980090137</v>
+        <v>0.115278687636521</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0945944794166881</v>
+        <v>0.117266307614709</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.151293083181801</v>
+        <v>-0.174332808119947</v>
       </c>
       <c r="E16" t="n">
-        <v>0.00757416009827086</v>
+        <v>-0.0529547637641877</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0244552663377533</v>
+        <v>-0.040320957103986</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0467212853813919</v>
+        <v>-0.0111037965175065</v>
       </c>
       <c r="H16" t="n">
-        <v>0.120620914139684</v>
+        <v>-0.0796522634466623</v>
       </c>
       <c r="I16" t="n">
-        <v>0.25594090762474</v>
+        <v>-0.138850483188957</v>
       </c>
       <c r="J16" t="n">
-        <v>0.307468748521002</v>
+        <v>0.376510896837548</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0676327466349073</v>
+        <v>0.00529921345288856</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.218860509442088</v>
+        <v>-0.223111466558148</v>
       </c>
       <c r="M16" t="n">
-        <v>0.169385191482912</v>
+        <v>0.167234045059127</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0678834266741262</v>
+        <v>-0.0751127613137639</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.242373176139405</v>
+        <v>0.525942463292268</v>
       </c>
     </row>
     <row r="17">
@@ -1211,46 +1211,46 @@
         <v>30</v>
       </c>
       <c r="B17" t="n">
-        <v>0.275814164179018</v>
+        <v>0.276651960782342</v>
       </c>
       <c r="C17" t="n">
-        <v>-0.237524343412188</v>
+        <v>-0.236912997666884</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.00745780166748161</v>
+        <v>-0.0169661240993072</v>
       </c>
       <c r="E17" t="n">
-        <v>0.158994250931865</v>
+        <v>0.171027597920858</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0122168432228338</v>
+        <v>0.0242123977722134</v>
       </c>
       <c r="G17" t="n">
-        <v>0.158207053372805</v>
+        <v>0.20798433686239</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.141393630461808</v>
+        <v>0.0955571612444445</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.0700331775058513</v>
+        <v>0.0347640416312321</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.0135652825865529</v>
+        <v>0.00850567987268043</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0783743832598784</v>
+        <v>0.062403008408698</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.244167962923406</v>
+        <v>-0.240502000835411</v>
       </c>
       <c r="M17" t="n">
-        <v>0.115069899679326</v>
+        <v>0.10967043852133</v>
       </c>
       <c r="N17" t="n">
-        <v>0.131671944323397</v>
+        <v>0.142710104511462</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.0694956212355509</v>
+        <v>0.0444711665102833</v>
       </c>
     </row>
     <row r="18">
@@ -1258,46 +1258,46 @@
         <v>31</v>
       </c>
       <c r="B18" t="n">
-        <v>0.145339155313546</v>
+        <v>0.148039395645731</v>
       </c>
       <c r="C18" t="n">
-        <v>-0.0674987163592472</v>
+        <v>-0.0641365528209727</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.219206723109521</v>
+        <v>-0.215334490715395</v>
       </c>
       <c r="E18" t="n">
-        <v>0.135207539392561</v>
+        <v>0.181454471240034</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.263298672547318</v>
+        <v>-0.241875500553571</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.222612395229574</v>
+        <v>-0.223950026729497</v>
       </c>
       <c r="H18" t="n">
-        <v>0.15981299531325</v>
+        <v>-0.132054805046338</v>
       </c>
       <c r="I18" t="n">
-        <v>0.236491601563914</v>
+        <v>-0.214451827101865</v>
       </c>
       <c r="J18" t="n">
-        <v>0.176834267044835</v>
+        <v>0.272347063556133</v>
       </c>
       <c r="K18" t="n">
-        <v>0.187357780947447</v>
+        <v>0.120160222444956</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0619210266005432</v>
+        <v>0.0944418851777116</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.121526813427054</v>
+        <v>-0.110712411451209</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.2164160898228</v>
+        <v>-0.173687203174489</v>
       </c>
       <c r="O18" t="n">
-        <v>0.137329240096882</v>
+        <v>-0.160006349302111</v>
       </c>
     </row>
     <row r="19">
@@ -1305,46 +1305,46 @@
         <v>32</v>
       </c>
       <c r="B19" t="n">
-        <v>0.118720868348221</v>
+        <v>0.108335700150131</v>
       </c>
       <c r="C19" t="n">
-        <v>-0.0702180896730348</v>
+        <v>-0.050000263946987</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.00262473429142883</v>
+        <v>-0.0344597069345822</v>
       </c>
       <c r="E19" t="n">
-        <v>0.112809168709506</v>
+        <v>0.0635032589284973</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.0212007554496724</v>
+        <v>-0.0309326549330949</v>
       </c>
       <c r="G19" t="n">
-        <v>0.0830897094220322</v>
+        <v>0.0546966184547378</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0885724243755241</v>
+        <v>-0.0779734923113725</v>
       </c>
       <c r="I19" t="n">
-        <v>0.13285111810426</v>
+        <v>-0.0978681954087723</v>
       </c>
       <c r="J19" t="n">
-        <v>0.0669125564245377</v>
+        <v>0.121572762787166</v>
       </c>
       <c r="K19" t="n">
-        <v>0.08768816951633</v>
+        <v>0.0674559794968847</v>
       </c>
       <c r="L19" t="n">
-        <v>0.199742435560485</v>
+        <v>0.177856030481413</v>
       </c>
       <c r="M19" t="n">
-        <v>0.32580783999144</v>
+        <v>0.331352855160074</v>
       </c>
       <c r="N19" t="n">
-        <v>0.55079778598757</v>
+        <v>0.5550191838502</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.279167221210723</v>
+        <v>-0.408900216608421</v>
       </c>
     </row>
     <row r="20">
@@ -1352,46 +1352,46 @@
         <v>33</v>
       </c>
       <c r="B20" t="n">
-        <v>0.259680876775407</v>
+        <v>0.259124578956307</v>
       </c>
       <c r="C20" t="n">
-        <v>-0.295061338319742</v>
+        <v>-0.289419570111147</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.0431779618025824</v>
+        <v>-0.0588420455075382</v>
       </c>
       <c r="E20" t="n">
-        <v>0.346548696971334</v>
+        <v>0.386848143984349</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0246642251819949</v>
+        <v>0.00541956690653946</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.206589433209265</v>
+        <v>-0.153846154079177</v>
       </c>
       <c r="H20" t="n">
-        <v>0.00172929303744773</v>
+        <v>-0.0182903763294374</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0122322647174007</v>
+        <v>-0.0492962338521912</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.237170125191476</v>
+        <v>-0.26115497688166</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.426174177982837</v>
+        <v>-0.416545126338111</v>
       </c>
       <c r="L20" t="n">
-        <v>0.144527026903605</v>
+        <v>0.169199491203654</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.0286329543404284</v>
+        <v>0.00652811976154438</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.217506054355344</v>
+        <v>-0.194143984986188</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.10277999498754</v>
+        <v>0.111288361743764</v>
       </c>
     </row>
     <row r="21">
@@ -1399,46 +1399,46 @@
         <v>34</v>
       </c>
       <c r="B21" t="n">
-        <v>0.159135599356526</v>
+        <v>0.158221148166019</v>
       </c>
       <c r="C21" t="n">
-        <v>-0.0952818793071476</v>
+        <v>-0.0911942331493307</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.0659613507267245</v>
+        <v>-0.0733632697539495</v>
       </c>
       <c r="E21" t="n">
-        <v>0.035705575448106</v>
+        <v>0.0533194415612919</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.314450692878198</v>
+        <v>-0.311143213474281</v>
       </c>
       <c r="G21" t="n">
-        <v>0.0572388896269371</v>
+        <v>0.0529847839983312</v>
       </c>
       <c r="H21" t="n">
-        <v>0.043530579241622</v>
+        <v>-0.0412389999525255</v>
       </c>
       <c r="I21" t="n">
-        <v>0.144218909146718</v>
+        <v>-0.177609740784177</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.0967460240855595</v>
+        <v>-0.0460341872794184</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.0830921955722669</v>
+        <v>-0.102579114831951</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.202351285295147</v>
+        <v>-0.175974515462603</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.568026717002782</v>
+        <v>-0.574330123556652</v>
       </c>
       <c r="N21" t="n">
-        <v>0.209154797492692</v>
+        <v>0.173344818028868</v>
       </c>
       <c r="O21" t="n">
-        <v>0.0557573885947905</v>
+        <v>0.115718083503853</v>
       </c>
     </row>
     <row r="22">
@@ -1446,46 +1446,46 @@
         <v>35</v>
       </c>
       <c r="B22" t="n">
-        <v>0.162778096759559</v>
+        <v>0.152787386058832</v>
       </c>
       <c r="C22" t="n">
-        <v>-0.156414327179443</v>
+        <v>-0.137824586376396</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.0237774801997158</v>
+        <v>-0.0559835762338327</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.126612377416408</v>
+        <v>-0.208462880053805</v>
       </c>
       <c r="F22" t="n">
-        <v>0.203311596912646</v>
+        <v>0.170529201946443</v>
       </c>
       <c r="G22" t="n">
-        <v>0.157501218584994</v>
+        <v>0.101814352796228</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.167798758571628</v>
+        <v>0.212738991389158</v>
       </c>
       <c r="I22" t="n">
-        <v>0.329555655133222</v>
+        <v>-0.172835883832171</v>
       </c>
       <c r="J22" t="n">
-        <v>0.199051961647002</v>
+        <v>0.205556918039189</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.484864785814726</v>
+        <v>-0.527536272129893</v>
       </c>
       <c r="L22" t="n">
-        <v>0.380318840174791</v>
+        <v>0.393291915658486</v>
       </c>
       <c r="M22" t="n">
-        <v>0.0622325029136213</v>
+        <v>0.107736182081379</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.138380705679686</v>
+        <v>-0.131760437413266</v>
       </c>
       <c r="O22" t="n">
-        <v>0.294224491711368</v>
+        <v>0.0440212788657281</v>
       </c>
     </row>
     <row r="23">
@@ -1493,46 +1493,46 @@
         <v>36</v>
       </c>
       <c r="B23" t="n">
-        <v>0.161589330464693</v>
+        <v>0.164737001756311</v>
       </c>
       <c r="C23" t="n">
-        <v>-0.433819869658525</v>
+        <v>-0.44281713307566</v>
       </c>
       <c r="D23" t="n">
-        <v>0.113831094227598</v>
+        <v>0.10476123787101</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.0530742949290581</v>
+        <v>-0.0120428852219869</v>
       </c>
       <c r="F23" t="n">
-        <v>0.0456630449007295</v>
+        <v>0.0464141512740765</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.0666785131883262</v>
+        <v>-0.0247160160881914</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.36044929054247</v>
+        <v>0.345381405350216</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.270295922520253</v>
+        <v>0.403459317903965</v>
       </c>
       <c r="J23" t="n">
-        <v>0.44391363034526</v>
+        <v>0.348833900829294</v>
       </c>
       <c r="K23" t="n">
-        <v>0.210187285700342</v>
+        <v>0.204958138935256</v>
       </c>
       <c r="L23" t="n">
-        <v>0.108042559207978</v>
+        <v>0.101380305638861</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.042417068484735</v>
+        <v>-0.0518184841794709</v>
       </c>
       <c r="N23" t="n">
-        <v>0.148775196682363</v>
+        <v>0.143218516709989</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0293950711900953</v>
+        <v>0.0590279228689319</v>
       </c>
     </row>
     <row r="24">
@@ -1540,46 +1540,46 @@
         <v>37</v>
       </c>
       <c r="B24" t="n">
-        <v>0.242625712743089</v>
+        <v>0.239531393365342</v>
       </c>
       <c r="C24" t="n">
-        <v>-0.156781818638575</v>
+        <v>-0.149016876846476</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0207468132557925</v>
+        <v>0.00342394976238209</v>
       </c>
       <c r="E24" t="n">
-        <v>0.169682046910329</v>
+        <v>0.151513291291156</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0262250268834016</v>
+        <v>0.0303211578171265</v>
       </c>
       <c r="G24" t="n">
-        <v>0.237978951606792</v>
+        <v>0.255027031234592</v>
       </c>
       <c r="H24" t="n">
-        <v>0.275715905489834</v>
+        <v>-0.339576437676604</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.263047846416108</v>
+        <v>0.18486553492461</v>
       </c>
       <c r="J24" t="n">
-        <v>0.00433479490687868</v>
+        <v>0.0128698376781155</v>
       </c>
       <c r="K24" t="n">
-        <v>0.217205977593074</v>
+        <v>0.207456178016546</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.203852140337</v>
+        <v>-0.19150409398834</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.140940968554306</v>
+        <v>-0.131331114289047</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.258427380190702</v>
+        <v>-0.278440180998825</v>
       </c>
       <c r="O24" t="n">
-        <v>0.217244617915519</v>
+        <v>-0.118290019879757</v>
       </c>
     </row>
   </sheetData>
